--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_ESET ONTINET.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_ESET ONTINET.xlsx
@@ -565,13 +565,13 @@
         <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>78.61709999999999</v>
+        <v>46.7394</v>
       </c>
       <c r="E2" t="n">
-        <v>51.3837</v>
+        <v>31.0245</v>
       </c>
       <c r="F2" t="n">
-        <v>27.2337</v>
+        <v>15.7142</v>
       </c>
       <c r="G2" t="n">
         <v>23.9436</v>
@@ -610,13 +610,13 @@
         <v>43.5897</v>
       </c>
       <c r="S2" t="n">
-        <v>53.0007</v>
+        <v>21.1227</v>
       </c>
       <c r="T2" t="n">
-        <v>29.5232</v>
+        <v>9.164300000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>23.4774</v>
+        <v>11.9583</v>
       </c>
       <c r="V2" t="n">
         <v>13.1837</v>
@@ -643,13 +643,13 @@
         <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>26.3889</v>
+        <v>29.9334</v>
       </c>
       <c r="E3" t="n">
-        <v>20.9038</v>
+        <v>20.4217</v>
       </c>
       <c r="F3" t="n">
-        <v>5.4846</v>
+        <v>9.5116</v>
       </c>
       <c r="G3" t="n">
         <v>22.9291</v>
@@ -688,13 +688,13 @@
         <v>41.8914</v>
       </c>
       <c r="S3" t="n">
-        <v>3.6753</v>
+        <v>7.2199</v>
       </c>
       <c r="T3" t="n">
-        <v>2.9682</v>
+        <v>2.4861</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7075000000000001</v>
+        <v>4.734</v>
       </c>
       <c r="V3" t="n">
         <v>7.3325</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. CABRERA GUEDES</t>
+          <t>A. VALDERRAMA CARRENO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D7" t="n">
-        <v>8.3963</v>
+        <v>5.2545</v>
       </c>
       <c r="E7" t="n">
-        <v>7.833</v>
+        <v>5.730600000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5634000000000001</v>
+        <v>-0.4759999999999995</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4986000000000015</v>
+        <v>-12.316</v>
       </c>
       <c r="H7" t="n">
-        <v>-6.908100000000001</v>
+        <v>-5.4722</v>
       </c>
       <c r="I7" t="n">
-        <v>7.4067</v>
+        <v>-6.8435</v>
       </c>
       <c r="J7" t="n">
-        <v>19.3332</v>
+        <v>4.8941</v>
       </c>
       <c r="K7" t="n">
-        <v>9.0097</v>
+        <v>7.2399</v>
       </c>
       <c r="L7" t="n">
-        <v>10.3237</v>
+        <v>-2.3455</v>
       </c>
       <c r="M7" t="n">
-        <v>-18.8347</v>
+        <v>-17.2101</v>
       </c>
       <c r="N7" t="n">
-        <v>-15.9178</v>
+        <v>-12.7122</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.9172</v>
+        <v>-4.4979</v>
       </c>
       <c r="P7" t="n">
-        <v>-5.661</v>
+        <v>-0.1886999999999995</v>
       </c>
       <c r="Q7" t="n">
-        <v>-25.0971</v>
+        <v>-22.644</v>
       </c>
       <c r="R7" t="n">
-        <v>19.4361</v>
+        <v>22.4553</v>
       </c>
       <c r="S7" t="n">
-        <v>17.0872</v>
+        <v>0.9504000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>8.7867</v>
+        <v>1.2944</v>
       </c>
       <c r="U7" t="n">
-        <v>8.300699999999999</v>
+        <v>-0.3440000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>-3.5288</v>
+        <v>16.8089</v>
       </c>
       <c r="W7" t="n">
-        <v>4.809800000000001</v>
+        <v>22.1856</v>
       </c>
       <c r="X7" t="n">
-        <v>-8.3386</v>
+        <v>-5.3768</v>
       </c>
     </row>
     <row r="8">
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. HERNANDEZ SELLES</t>
+          <t>J. SANTONJA FERRERO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3823</v>
+        <v>3.453</v>
       </c>
       <c r="E9" t="n">
-        <v>1.275</v>
+        <v>8.659500000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1073</v>
+        <v>-5.2064</v>
       </c>
       <c r="G9" t="n">
-        <v>1.1936</v>
+        <v>-2.474299999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2113</v>
+        <v>2.4137</v>
       </c>
       <c r="I9" t="n">
-        <v>1.4049</v>
+        <v>-4.888100000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>1.275</v>
+        <v>22.7105</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>19.7697</v>
       </c>
       <c r="L9" t="n">
-        <v>1.275</v>
+        <v>2.9408</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0814</v>
+        <v>-25.1847</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2113</v>
+        <v>-17.3558</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1299</v>
+        <v>-7.8288</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1887</v>
+        <v>0.1887000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-26.2293</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1887</v>
+        <v>26.418</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>0.6370000000000002</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>-1.745</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.3821</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>5.1016</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>13.923</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-8.821400000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. VALDERRAMA CARRENO</t>
+          <t>N. HERNANDEZ SELLES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,70 +1186,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.09120000000000106</v>
+        <v>1.3823</v>
       </c>
       <c r="E10" t="n">
-        <v>2.747</v>
+        <v>1.275</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.8382</v>
+        <v>0.1073</v>
       </c>
       <c r="G10" t="n">
-        <v>-12.316</v>
+        <v>1.1936</v>
       </c>
       <c r="H10" t="n">
-        <v>-5.4722</v>
+        <v>-0.2113</v>
       </c>
       <c r="I10" t="n">
-        <v>-6.8435</v>
+        <v>1.4049</v>
       </c>
       <c r="J10" t="n">
-        <v>4.8941</v>
+        <v>1.275</v>
       </c>
       <c r="K10" t="n">
-        <v>7.2399</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.3455</v>
+        <v>1.275</v>
       </c>
       <c r="M10" t="n">
-        <v>-17.2101</v>
+        <v>-0.0814</v>
       </c>
       <c r="N10" t="n">
-        <v>-12.7122</v>
+        <v>-0.2113</v>
       </c>
       <c r="O10" t="n">
-        <v>-4.4979</v>
+        <v>0.1299</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1886999999999995</v>
+        <v>0.1887</v>
       </c>
       <c r="Q10" t="n">
-        <v>-22.644</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>22.4553</v>
+        <v>0.1887</v>
       </c>
       <c r="S10" t="n">
-        <v>-4.3952</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.6892</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>-2.7066</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>16.8089</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>22.1856</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-5.3768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2302</v>
+        <v>-0.2928</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0999</v>
+        <v>-0.095</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3301</v>
+        <v>-0.1978</v>
       </c>
       <c r="G11" t="n">
         <v>0.0808</v>
@@ -1312,13 +1312,13 @@
         <v>0.1887</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4438</v>
+        <v>0.3812</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3556</v>
+        <v>0.1608</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0882</v>
+        <v>0.2205</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.5344</v>
+        <v>-0.5609</v>
       </c>
       <c r="E12" t="n">
         <v>-0.2851</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2493</v>
+        <v>-0.2757</v>
       </c>
       <c r="G12" t="n">
         <v>0.1182</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1587</v>
+        <v>0.1323</v>
       </c>
       <c r="T12" t="n">
         <v>-0.1176</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2763</v>
+        <v>0.2498</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6226</v>
@@ -1423,10 +1423,10 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.7645999999999999</v>
+        <v>-0.5698</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.2516</v>
+        <v>-0.0568</v>
       </c>
       <c r="F13" t="n">
         <v>-0.513</v>
@@ -1468,13 +1468,13 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3897</v>
+        <v>-0.1949</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.294</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.09580000000000001</v>
+        <v>-0.0958</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>I. CAMBRA DOBRE</t>
+          <t>D. CABRERA GUEDES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.0824</v>
+        <v>-1.068499999999998</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.2723</v>
+        <v>1.072899999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8100999999999999</v>
+        <v>-2.1413</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.2869000000000002</v>
+        <v>0.4986000000000015</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.0142</v>
+        <v>-6.908100000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7273000000000001</v>
+        <v>7.4067</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1415000000000001</v>
+        <v>19.3332</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.6073999999999999</v>
+        <v>9.0097</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7488999999999999</v>
+        <v>10.3237</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.4286</v>
+        <v>-18.8347</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.407</v>
+        <v>-15.9178</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.02160000000000001</v>
+        <v>-2.9172</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.5661</v>
+        <v>-5.661</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9435</v>
+        <v>-25.0971</v>
       </c>
       <c r="R14" t="n">
-        <v>0.3774</v>
+        <v>19.4361</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6067</v>
+        <v>7.622299999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4704</v>
+        <v>2.027</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1364</v>
+        <v>5.595800000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.6226</v>
+        <v>-3.5288</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>4.809800000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.6226</v>
+        <v>-8.3386</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V. CAMBRA NADAL</t>
+          <t>I. CAMBRA DOBRE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>-3.3466</v>
+        <v>-1.7023</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.1745</v>
+        <v>-1.0774</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1721</v>
+        <v>-0.6249</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1122</v>
+        <v>-0.2869000000000002</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.3516</v>
+        <v>-1.0142</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4636</v>
+        <v>0.7273000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1626000000000003</v>
+        <v>0.1415000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.5861999999999999</v>
+        <v>-0.6073999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7488</v>
+        <v>0.7488999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.05059999999999998</v>
+        <v>-0.4286</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7655000000000001</v>
+        <v>-0.407</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7145999999999999</v>
+        <v>-0.02160000000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.5096</v>
+        <v>-0.5661</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.8305</v>
+        <v>-0.9435</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3209</v>
+        <v>0.3774</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.3455</v>
+        <v>-0.2266</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7521</v>
+        <v>-0.2755</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5938</v>
+        <v>0.0489</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.6036000000000001</v>
+        <v>-0.6226</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.8488</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. MARTINEZ SANTOS</t>
+          <t>V. CAMBRA NADAL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,70 +1654,70 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>-5.8875</v>
+        <v>-2.2375</v>
       </c>
       <c r="E16" t="n">
-        <v>-5.9921</v>
+        <v>-1.5898</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1046000000000001</v>
+        <v>-0.6477999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.1383</v>
+        <v>0.1122</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.7462</v>
+        <v>-1.3516</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6079000000000001</v>
+        <v>1.4636</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3447</v>
+        <v>0.1626000000000003</v>
       </c>
       <c r="K16" t="n">
-        <v>1.7772</v>
+        <v>-0.5861999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.4324999999999999</v>
+        <v>0.7488</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.483</v>
+        <v>-0.05059999999999998</v>
       </c>
       <c r="N16" t="n">
-        <v>-4.5232</v>
+        <v>-0.7655000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>1.0404</v>
+        <v>0.7145999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.5660999999999998</v>
+        <v>-1.5096</v>
       </c>
       <c r="Q16" t="n">
-        <v>-6.4158</v>
+        <v>-2.8305</v>
       </c>
       <c r="R16" t="n">
-        <v>5.8497</v>
+        <v>1.3209</v>
       </c>
       <c r="S16" t="n">
-        <v>1.5296</v>
+        <v>-0.2365</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2795</v>
+        <v>-0.1673</v>
       </c>
       <c r="U16" t="n">
-        <v>1.809</v>
+        <v>-0.06920000000000003</v>
       </c>
       <c r="V16" t="n">
-        <v>-4.7128</v>
+        <v>-0.6036000000000001</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6415999999999999</v>
+        <v>1.2452</v>
       </c>
       <c r="X16" t="n">
-        <v>-4.0712</v>
+        <v>-1.8488</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>24</v>
       </c>
       <c r="D17" t="n">
-        <v>-7.210699999999999</v>
+        <v>-4.587499999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7494</v>
+        <v>3.389</v>
       </c>
       <c r="F17" t="n">
-        <v>-8.959999999999999</v>
+        <v>-7.9759</v>
       </c>
       <c r="G17" t="n">
         <v>-9.2491</v>
@@ -1780,13 +1780,13 @@
         <v>25.4745</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4747999999999998</v>
+        <v>3.0979</v>
       </c>
       <c r="T17" t="n">
-        <v>-2.1885</v>
+        <v>-0.5489000000000002</v>
       </c>
       <c r="U17" t="n">
-        <v>2.6629</v>
+        <v>3.6471</v>
       </c>
       <c r="V17" t="n">
         <v>-7.4935</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. SANTONJA FERRERO</t>
+          <t>J. MARTINEZ SANTOS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,70 +1810,70 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>-7.332100000000001</v>
+        <v>-5.974</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1978000000000018</v>
+        <v>-5.992100000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>-7.530099999999999</v>
+        <v>0.01819999999999977</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.474299999999999</v>
+        <v>-2.1383</v>
       </c>
       <c r="H18" t="n">
-        <v>2.4137</v>
+        <v>-2.7462</v>
       </c>
       <c r="I18" t="n">
-        <v>-4.888100000000001</v>
+        <v>0.6079000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>22.7105</v>
+        <v>1.3447</v>
       </c>
       <c r="K18" t="n">
-        <v>19.7697</v>
+        <v>1.7772</v>
       </c>
       <c r="L18" t="n">
-        <v>2.9408</v>
+        <v>-0.4324999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>-25.1847</v>
+        <v>-3.483</v>
       </c>
       <c r="N18" t="n">
-        <v>-17.3558</v>
+        <v>-4.5232</v>
       </c>
       <c r="O18" t="n">
-        <v>-7.8288</v>
+        <v>1.0404</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1887000000000001</v>
+        <v>-0.5660999999999998</v>
       </c>
       <c r="Q18" t="n">
-        <v>-26.2293</v>
+        <v>-6.4158</v>
       </c>
       <c r="R18" t="n">
-        <v>26.418</v>
+        <v>5.8497</v>
       </c>
       <c r="S18" t="n">
-        <v>-10.1483</v>
+        <v>1.4432</v>
       </c>
       <c r="T18" t="n">
-        <v>-10.2066</v>
+        <v>-0.2794</v>
       </c>
       <c r="U18" t="n">
-        <v>0.05840000000000023</v>
+        <v>1.7227</v>
       </c>
       <c r="V18" t="n">
-        <v>5.1016</v>
+        <v>-4.7128</v>
       </c>
       <c r="W18" t="n">
-        <v>13.923</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X18" t="n">
-        <v>-8.821400000000001</v>
+        <v>-4.0712</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>-10.2497</v>
+        <v>-10.2366</v>
       </c>
       <c r="E19" t="n">
-        <v>-9.542899999999999</v>
+        <v>-9.133100000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7067000000000001</v>
+        <v>-1.1035</v>
       </c>
       <c r="G19" t="n">
         <v>-2.8799</v>
@@ -1936,13 +1936,13 @@
         <v>2.8305</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3538000000000001</v>
+        <v>-0.3407</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.5256</v>
+        <v>-1.1157</v>
       </c>
       <c r="U19" t="n">
-        <v>1.1718</v>
+        <v>0.775</v>
       </c>
       <c r="V19" t="n">
         <v>-1.1663</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. TAENO ELEZ</t>
+          <t>J. MOLINA LORENZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,70 +1966,70 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="D20" t="n">
-        <v>-22.095</v>
+        <v>-10.5917</v>
       </c>
       <c r="E20" t="n">
-        <v>-17.1658</v>
+        <v>-4.243499999999998</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.929200000000001</v>
+        <v>-6.348100000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>1.143</v>
+        <v>24.7239</v>
       </c>
       <c r="H20" t="n">
-        <v>4.616499999999999</v>
+        <v>4.888500000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.4736</v>
+        <v>19.835</v>
       </c>
       <c r="J20" t="n">
-        <v>17.6843</v>
+        <v>48.499</v>
       </c>
       <c r="K20" t="n">
-        <v>14.4517</v>
+        <v>19.7985</v>
       </c>
       <c r="L20" t="n">
-        <v>3.2326</v>
+        <v>28.7007</v>
       </c>
       <c r="M20" t="n">
-        <v>-16.5413</v>
+        <v>-23.7756</v>
       </c>
       <c r="N20" t="n">
-        <v>-9.8354</v>
+        <v>-14.9095</v>
       </c>
       <c r="O20" t="n">
-        <v>-6.7061</v>
+        <v>-8.866</v>
       </c>
       <c r="P20" t="n">
-        <v>-24.1536</v>
+        <v>-22.2666</v>
       </c>
       <c r="Q20" t="n">
-        <v>-46.6089</v>
+        <v>-61.7049</v>
       </c>
       <c r="R20" t="n">
-        <v>22.4553</v>
+        <v>39.4383</v>
       </c>
       <c r="S20" t="n">
-        <v>-3.1472</v>
+        <v>0.285</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.7296</v>
+        <v>-2.7535</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.4177</v>
+        <v>3.0383</v>
       </c>
       <c r="V20" t="n">
-        <v>4.0627</v>
+        <v>-13.3339</v>
       </c>
       <c r="W20" t="n">
-        <v>13.4882</v>
+        <v>11.7154</v>
       </c>
       <c r="X20" t="n">
-        <v>-9.4255</v>
+        <v>-25.0493</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>23</v>
       </c>
       <c r="D21" t="n">
-        <v>-24.9098</v>
+        <v>-18.5209</v>
       </c>
       <c r="E21" t="n">
-        <v>-25.7878</v>
+        <v>-23.779</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8785000000000004</v>
+        <v>5.2578</v>
       </c>
       <c r="G21" t="n">
         <v>0.2678</v>
@@ -2092,13 +2092,13 @@
         <v>13.209</v>
       </c>
       <c r="S21" t="n">
-        <v>-5.5418</v>
+        <v>0.8469</v>
       </c>
       <c r="T21" t="n">
-        <v>-2.9324</v>
+        <v>-0.923</v>
       </c>
       <c r="U21" t="n">
-        <v>-2.6099</v>
+        <v>1.7701</v>
       </c>
       <c r="V21" t="n">
         <v>-1.3317</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. MOLINA LORENZ</t>
+          <t>M. TAENO ELEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2122,76 +2122,76 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D22" t="n">
-        <v>-26.1189</v>
+        <v>-18.8121</v>
       </c>
       <c r="E22" t="n">
-        <v>-13.8945</v>
+        <v>-16.1126</v>
       </c>
       <c r="F22" t="n">
-        <v>-12.2244</v>
+        <v>-2.699600000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>24.7239</v>
+        <v>1.143</v>
       </c>
       <c r="H22" t="n">
-        <v>4.888500000000001</v>
+        <v>4.616499999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>19.835</v>
+        <v>-3.4736</v>
       </c>
       <c r="J22" t="n">
-        <v>48.499</v>
+        <v>17.6843</v>
       </c>
       <c r="K22" t="n">
-        <v>19.7985</v>
+        <v>14.4517</v>
       </c>
       <c r="L22" t="n">
-        <v>28.7007</v>
+        <v>3.2326</v>
       </c>
       <c r="M22" t="n">
-        <v>-23.7756</v>
+        <v>-16.5413</v>
       </c>
       <c r="N22" t="n">
-        <v>-14.9095</v>
+        <v>-9.8354</v>
       </c>
       <c r="O22" t="n">
-        <v>-8.866</v>
+        <v>-6.7061</v>
       </c>
       <c r="P22" t="n">
-        <v>-22.2666</v>
+        <v>-24.1536</v>
       </c>
       <c r="Q22" t="n">
-        <v>-61.7049</v>
+        <v>-46.6089</v>
       </c>
       <c r="R22" t="n">
-        <v>39.4383</v>
+        <v>22.4553</v>
       </c>
       <c r="S22" t="n">
-        <v>-15.2421</v>
+        <v>0.1357</v>
       </c>
       <c r="T22" t="n">
-        <v>-12.4043</v>
+        <v>-0.6761999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>-2.8378</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>-13.3339</v>
+        <v>4.0627</v>
       </c>
       <c r="W22" t="n">
-        <v>11.7154</v>
+        <v>13.4882</v>
       </c>
       <c r="X22" t="n">
-        <v>-25.0493</v>
+        <v>-9.4255</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. IBANEZ TEJERO</t>
+          <t>N. RAMOS CAMPOS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2200,76 +2200,76 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="D23" t="n">
-        <v>-35.8902</v>
+        <v>-28.6239</v>
       </c>
       <c r="E23" t="n">
-        <v>-23.2686</v>
+        <v>-26.2431</v>
       </c>
       <c r="F23" t="n">
-        <v>-12.6214</v>
+        <v>-2.381000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>-21.0244</v>
+        <v>-15.4664</v>
       </c>
       <c r="H23" t="n">
-        <v>-9.666</v>
+        <v>-4.5804</v>
       </c>
       <c r="I23" t="n">
-        <v>-11.3587</v>
+        <v>-10.8861</v>
       </c>
       <c r="J23" t="n">
-        <v>-4.2279</v>
+        <v>7.8588</v>
       </c>
       <c r="K23" t="n">
-        <v>4.9496</v>
+        <v>8.795199999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>-9.177300000000001</v>
+        <v>-0.9365999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>-16.7967</v>
+        <v>-23.325</v>
       </c>
       <c r="N23" t="n">
-        <v>-14.6154</v>
+        <v>-13.3756</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.1812</v>
+        <v>-9.949400000000001</v>
       </c>
       <c r="P23" t="n">
-        <v>-19.6248</v>
+        <v>-13.3977</v>
       </c>
       <c r="Q23" t="n">
-        <v>-36.9852</v>
+        <v>-43.2123</v>
       </c>
       <c r="R23" t="n">
-        <v>17.3604</v>
+        <v>29.8146</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0663</v>
+        <v>-2.8212</v>
       </c>
       <c r="T23" t="n">
-        <v>2.2292</v>
+        <v>-3.9263</v>
       </c>
       <c r="U23" t="n">
-        <v>-3.2959</v>
+        <v>1.1054</v>
       </c>
       <c r="V23" t="n">
-        <v>5.8254</v>
+        <v>3.0612</v>
       </c>
       <c r="W23" t="n">
-        <v>15.7148</v>
+        <v>13.0366</v>
       </c>
       <c r="X23" t="n">
-        <v>-9.8894</v>
+        <v>-9.9754</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>N. RAMOS CAMPOS</t>
+          <t>J. IBANEZ TEJERO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2278,70 +2278,70 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D24" t="n">
-        <v>-44.3031</v>
+        <v>-34.2357</v>
       </c>
       <c r="E24" t="n">
-        <v>-35.1131</v>
+        <v>-25.3517</v>
       </c>
       <c r="F24" t="n">
-        <v>-9.190200000000001</v>
+        <v>-8.8841</v>
       </c>
       <c r="G24" t="n">
-        <v>-15.4664</v>
+        <v>-21.0244</v>
       </c>
       <c r="H24" t="n">
-        <v>-4.5804</v>
+        <v>-9.666</v>
       </c>
       <c r="I24" t="n">
-        <v>-10.8861</v>
+        <v>-11.3587</v>
       </c>
       <c r="J24" t="n">
-        <v>7.8588</v>
+        <v>-4.2279</v>
       </c>
       <c r="K24" t="n">
-        <v>8.795199999999999</v>
+        <v>4.9496</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.9365999999999999</v>
+        <v>-9.177300000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>-23.325</v>
+        <v>-16.7967</v>
       </c>
       <c r="N24" t="n">
-        <v>-13.3756</v>
+        <v>-14.6154</v>
       </c>
       <c r="O24" t="n">
-        <v>-9.949400000000001</v>
+        <v>-2.1812</v>
       </c>
       <c r="P24" t="n">
-        <v>-13.3977</v>
+        <v>-19.6248</v>
       </c>
       <c r="Q24" t="n">
-        <v>-43.2123</v>
+        <v>-36.9852</v>
       </c>
       <c r="R24" t="n">
-        <v>29.8146</v>
+        <v>17.3604</v>
       </c>
       <c r="S24" t="n">
-        <v>-18.5001</v>
+        <v>0.5882000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-12.7965</v>
+        <v>0.1462999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-5.7039</v>
+        <v>0.4416</v>
       </c>
       <c r="V24" t="n">
-        <v>3.0612</v>
+        <v>5.8254</v>
       </c>
       <c r="W24" t="n">
-        <v>13.0366</v>
+        <v>15.7148</v>
       </c>
       <c r="X24" t="n">
-        <v>-9.9754</v>
+        <v>-9.8894</v>
       </c>
     </row>
     <row r="25">
@@ -2359,16 +2359,16 @@
         <v>24</v>
       </c>
       <c r="D25" t="n">
-        <v>-28.37740000000003</v>
+        <v>-3.367199999999997</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.6743000000000023</v>
+        <v>5.498400000000011</v>
       </c>
       <c r="F25" t="n">
-        <v>-27.7027</v>
+        <v>-8.866000000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>56.68499999999998</v>
+        <v>56.68499999999999</v>
       </c>
       <c r="H25" t="n">
         <v>47.35590000000001</v>
@@ -2398,19 +2398,19 @@
         <v>-122.655</v>
       </c>
       <c r="Q25" t="n">
-        <v>-434.9535000000001</v>
+        <v>-434.9535</v>
       </c>
       <c r="R25" t="n">
         <v>312.2985</v>
       </c>
       <c r="S25" t="n">
-        <v>15.6334</v>
+        <v>40.6428</v>
       </c>
       <c r="T25" t="n">
-        <v>-3.523400000000006</v>
+        <v>2.6514</v>
       </c>
       <c r="U25" t="n">
-        <v>19.1544</v>
+        <v>37.9926</v>
       </c>
       <c r="V25" t="n">
         <v>21.96020000000001</v>
